--- a/outputs/ci_comparison.xlsx
+++ b/outputs/ci_comparison.xlsx
@@ -445,22 +445,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>4835.748992515832</v>
+        <v>4824.180017226528</v>
       </c>
       <c r="D2">
-        <v>4002.393910302596</v>
+        <v>3992.941414238919</v>
       </c>
       <c r="E2">
-        <v>5669.104074729067</v>
+        <v>5655.418620214138</v>
       </c>
       <c r="F2">
-        <v>4057.946689694876</v>
+        <v>4059.705275624462</v>
       </c>
       <c r="G2">
-        <v>5745.686506908462</v>
+        <v>5674.612517944301</v>
       </c>
       <c r="H2">
-        <v>3474</v>
+        <v>3483</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -474,22 +474,22 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>706.5145911586246</v>
+        <v>460.9000288101412</v>
       </c>
       <c r="D3">
-        <v>622.442442924625</v>
+        <v>393.1171145849509</v>
       </c>
       <c r="E3">
-        <v>790.5867393926243</v>
+        <v>528.6829430353315</v>
       </c>
       <c r="F3">
-        <v>632.065913030916</v>
+        <v>396.6704624027658</v>
       </c>
       <c r="G3">
-        <v>793.0403134932099</v>
+        <v>532.6171708441371</v>
       </c>
       <c r="H3">
-        <v>3461</v>
+        <v>3471</v>
       </c>
       <c r="I3" t="s">
         <v>11</v>
@@ -503,22 +503,22 @@
         <v>15</v>
       </c>
       <c r="C4">
-        <v>162.891317016317</v>
+        <v>85.17401325266493</v>
       </c>
       <c r="D4">
-        <v>133.3339917246016</v>
+        <v>60.17171964401201</v>
       </c>
       <c r="E4">
-        <v>192.4486423080324</v>
+        <v>110.1763068613179</v>
       </c>
       <c r="F4">
-        <v>135.8932619463869</v>
+        <v>63.00834053586863</v>
       </c>
       <c r="G4">
-        <v>192.2629443473193</v>
+        <v>110.7488259867473</v>
       </c>
       <c r="H4">
-        <v>3432</v>
+        <v>3471</v>
       </c>
       <c r="I4" t="s">
         <v>11</v>
@@ -571,22 +571,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>50.33183937823834</v>
+        <v>50.20596899224806</v>
       </c>
       <c r="D2">
-        <v>45.51596399957864</v>
+        <v>45.40202254434708</v>
       </c>
       <c r="E2">
-        <v>55.14771475689805</v>
+        <v>55.00991544014904</v>
       </c>
       <c r="F2">
-        <v>45.81548049798504</v>
+        <v>45.68697071490094</v>
       </c>
       <c r="G2">
-        <v>55.69544998560736</v>
+        <v>55.05774038185473</v>
       </c>
       <c r="H2">
-        <v>3474</v>
+        <v>3483</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -600,22 +600,22 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>11.35055475296157</v>
+        <v>6.498403918179199</v>
       </c>
       <c r="D3">
-        <v>10.30797977556983</v>
+        <v>5.782815803674758</v>
       </c>
       <c r="E3">
-        <v>12.39312973035332</v>
+        <v>7.21399203268364</v>
       </c>
       <c r="F3">
-        <v>10.33157808436868</v>
+        <v>5.851520455200231</v>
       </c>
       <c r="G3">
-        <v>12.4082973851488</v>
+        <v>7.214393186401614</v>
       </c>
       <c r="H3">
-        <v>3461</v>
+        <v>3471</v>
       </c>
       <c r="I3" t="s">
         <v>11</v>
@@ -629,22 +629,22 @@
         <v>15</v>
       </c>
       <c r="C4">
-        <v>3.219050116550116</v>
+        <v>1.284422356669548</v>
       </c>
       <c r="D4">
-        <v>2.846758455047681</v>
+        <v>1.011273824137208</v>
       </c>
       <c r="E4">
-        <v>3.591341778052552</v>
+        <v>1.557570889201888</v>
       </c>
       <c r="F4">
-        <v>2.853799460955711</v>
+        <v>1.04086452031115</v>
       </c>
       <c r="G4">
-        <v>3.603564903846153</v>
+        <v>1.56852758571017</v>
       </c>
       <c r="H4">
-        <v>3432</v>
+        <v>3471</v>
       </c>
       <c r="I4" t="s">
         <v>11</v>
